--- a/public/share/data/比赛记录.xlsx
+++ b/public/share/data/比赛记录.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,10 @@
     </font>
     <font>
       <color rgb="00CC0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -153,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1490,42 +1495,1054 @@
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>📌 赛程变动</t>
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ 2026-07-19  中乙第17轮  🏟客场 vs 大连英博B  2-1 胜  总95′(90+5补时)  ⚽ 张俊哲40′·帕尔曼江90+4′</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>7/11(周五) vs 海港B — 台风延期</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>7/14(周一) vs 海港B(补) — 再次推迟，日期待定</t>
-        </is>
-      </c>
-    </row>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  26′ ↓何麟立 ↓巫林峰 ↑阿西江 ↑努尔扎提  |  69′ ↑陈少豪 ↑栾昊  |  85′ ↓陈祥煜  |  90+5′ ↑王捷</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>7/19(周六) vs 大连英博B(客) — 待进行</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>出场(min)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>首发/替补</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  首发 11人</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>95</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>760</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>脚踝痛但扛满全场✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>95</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>950</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>⚽ 进球 40′</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>95</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" t="n">
+        <v>665</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>95</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>760</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>95</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>855</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>69</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>483</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>26′↓</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>69</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>483</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>26′↓</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>脚掌OK✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>95</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" t="n">
+        <v>950</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>85</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>765</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>85′↓</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班(C)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>95</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" t="n">
+        <v>950</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>左后群微紧⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>95</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" t="n">
+        <v>950</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>⚽ 绝杀 90+4′</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  替补出场 5人</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>26</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>208</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>26′↑</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>26</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>182</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>26′↑</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>69′↑</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>69′↑</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>90+5′↑</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  替补未出场 6人</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>50</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>50</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>75</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>75</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" t="n">
+        <v>75</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>25</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>热身+替补席</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  未进大名单/未随队 7人</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>停赛(累计黄牌)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>停赛(累计黄牌)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>伤停</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>MCL撕裂·康复中</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>太原基地</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="A64:I64"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A44:I44"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/share/data/比赛记录.xlsx
+++ b/public/share/data/比赛记录.xlsx
@@ -2,25 +2,221 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="比赛记录" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="33">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF992828"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF992828"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFCC0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -28,16 +224,8 @@
     <font>
       <name val="PingFang SC"/>
       <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
+      <color rgb="00992828"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="PingFang SC"/>
@@ -51,17 +239,14 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00CC0000"/>
+      <name val="PingFang SC"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -70,24 +255,228 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-        <bgColor rgb="00E3F2FD"/>
+        <fgColor rgb="FF992828"/>
+        <bgColor rgb="FF992828"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-        <bgColor rgb="00FFF3E0"/>
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
+        <fgColor rgb="FF2C3E50"/>
+        <bgColor rgb="FF2C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+        <bgColor rgb="FFE3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00992828"/>
+        <bgColor rgb="00992828"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -97,23 +486,161 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -121,10 +648,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -133,52 +660,342 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -531,7 +1348,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -541,970 +1357,1509 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I163"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>比赛记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▸ 2026-07-08  中乙预赛第12轮  🏟主场  vs 大连可为  2-0  加时4min</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="10" t="n"/>
+          <t>崇德荣海 · 比赛记录 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.6" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>⚽ 7/8 中乙第12轮 · 主场 vs 大连可为 · 2-0 胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  79′ ↑何麟立 ↑阿西江-白山  ↓巫林峰 ↓凌中阳  |  81′ ↑陈少豪  ↓王捷(U21)  |  86′ ↑李金羽  ↓张天龙</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="10" t="n"/>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+          <t>首发11人</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>⚽40′</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>81′↓</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>左膝⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>86′↓</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>艾沙江(C)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>79′↓</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>79′↓</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>⚽90+4′</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>王皓文</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>替补4人</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>79′↑</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>79′↑</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>81′↑</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>86′↑</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>右膝⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>79′↑</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="17.6" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>⚽ 7/19 中乙第17轮 · 客场 vs 大连英博B · 2-1 胜（95min）</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>球员</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>出场(min)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>首发/替补</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>RPE</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>sRPE</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>换人</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  首发 11人</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="10" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>首发11人</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>张海轩</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>810</v>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>脚踝✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>⚽40′</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>王皓文</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>26′↓</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>26′↓</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>脚掌✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>张辉</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>张俊哲</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>810</v>
-      </c>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>进球 40′</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>85′↓</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>艾沙江(C)</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>后群⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>⚽90+4′</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>替补5人</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>26′↑</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="10" t="inlineStr"/>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>努尔扎提</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>26′↑</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>69′↑</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="10" t="inlineStr"/>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>69′↑</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>王捷(U21)</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>729</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>81′↓</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>左膝疼痛 ⚠️</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>张天龙</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>774</v>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>86′↓</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>艾沙江-库尔班 (C)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>巫林峰</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>790</v>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>79′↓</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>凌中阳</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>711</v>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>79′↓</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>帕尔曼江-克尤木</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>进球 90+4′</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>王皓文(U21)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>小腿酸痛</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>陈祥煜</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>首发</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  替补出场 4人</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>何麟立</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>替补</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>79′↑</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>阿西江-白山</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>79′↑</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>陈少豪</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>81′↑</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>李金羽</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>86′↑</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>右膝不适 ⚠️</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  替补未出场 7人</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>杨卓燠</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>王款(U21)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>杨翼璇</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>谢锦政</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>栾昊(U21)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>林楷轩(U21)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>未上场未填RPE；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>戚博(U21)</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>替补</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>未上场；赛后大禁区跑10趟</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  未进大名单 3人</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>朱云天(U21)</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>未进名单</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>丁云峰</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>未进名单</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>黄牌停赛</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>布格拉汗-斯坎旦尔</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>伤停</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>MCL撕裂</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▸ 2026-07-19  中乙第17轮  🏟客场 vs 大连英博B  2-1 胜  总95′(90+5补时)  ⚽ 张俊哲40′·帕尔曼江90+4′</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  26′ ↓何麟立 ↓巫林峰 ↑阿西江 ↑努尔扎提  |  69′ ↑陈少豪 ↑栾昊  |  85′ ↓陈祥煜  |  90+5′ ↑王捷</t>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>90+5′↑</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>左膝</t>
         </is>
       </c>
     </row>
@@ -1576,7 +2931,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1593,7 +2948,6 @@
       <c r="G45" t="n">
         <v>760</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>脚踝痛但扛满全场✅</t>
@@ -1613,7 +2967,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1630,7 +2984,6 @@
       <c r="G46" t="n">
         <v>950</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>⚽ 进球 40′</t>
@@ -1650,7 +3003,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1667,8 +3020,6 @@
       <c r="G47" t="n">
         <v>665</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1683,7 +3034,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1700,8 +3051,6 @@
       <c r="G48" t="n">
         <v>760</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1716,7 +3065,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1733,8 +3082,6 @@
       <c r="G49" t="n">
         <v>855</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1749,7 +3096,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1771,7 +3118,6 @@
           <t>26′↓</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1786,7 +3132,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1827,7 +3173,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1844,8 +3190,6 @@
       <c r="G52" t="n">
         <v>950</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1860,7 +3204,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1882,7 +3226,6 @@
           <t>85′↓</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1897,7 +3240,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1914,7 +3257,6 @@
       <c r="G54" t="n">
         <v>950</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>左后群微紧⚠️</t>
@@ -1934,7 +3276,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1951,7 +3293,6 @@
       <c r="G55" t="n">
         <v>950</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>⚽ 绝杀 90+4′</t>
@@ -1967,7 +3308,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>阿西江-白山</t>
@@ -1975,7 +3315,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1997,10 +3337,8 @@
           <t>26′↑</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>努尔扎提-努尔兰</t>
@@ -2008,7 +3346,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2030,10 +3368,8 @@
           <t>26′↑</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>陈少豪</t>
@@ -2041,7 +3377,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2063,10 +3399,8 @@
           <t>69′↑</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>栾昊(U21)</t>
@@ -2074,7 +3408,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2096,10 +3430,8 @@
           <t>69′↑</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>王捷(U21)</t>
@@ -2107,7 +3439,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2144,7 +3476,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>杨卓燠</t>
@@ -2152,10 +3483,9 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2167,7 +3497,6 @@
       <c r="G65" t="n">
         <v>50</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2175,7 +3504,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>王款(U21)</t>
@@ -2183,10 +3511,9 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2198,7 +3525,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2206,7 +3532,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>杨文杰</t>
@@ -2214,10 +3539,9 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2229,7 +3553,6 @@
       <c r="G67" t="n">
         <v>75</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2237,7 +3560,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr"/>
+      <c r="A68" s="19" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>谢锦政</t>
@@ -2245,10 +3568,9 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2260,7 +3582,6 @@
       <c r="G68" t="n">
         <v>75</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2268,7 +3589,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr"/>
+      <c r="A69" s="20" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>杨翼璇</t>
@@ -2276,10 +3597,9 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2291,7 +3611,6 @@
       <c r="G69" t="n">
         <v>75</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2299,7 +3618,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr"/>
+      <c r="A70" s="20" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>林楷轩(U21)</t>
@@ -2307,10 +3626,9 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>替补</t>
@@ -2322,7 +3640,6 @@
       <c r="G70" t="n">
         <v>25</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>热身+替补席</t>
@@ -2330,7 +3647,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr"/>
+      <c r="A71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2340,7 +3657,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>凌中阳</t>
@@ -2348,18 +3664,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>停赛(累计黄牌)</t>
@@ -2367,7 +3679,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>丁云峰</t>
@@ -2375,18 +3686,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>停赛(累计黄牌)</t>
@@ -2394,7 +3701,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>刘子洁</t>
@@ -2402,18 +3708,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>太原基地</t>
@@ -2421,7 +3723,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>朱云天(U21)</t>
@@ -2429,18 +3730,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>太原基地</t>
@@ -2448,7 +3745,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>董德</t>
@@ -2456,18 +3752,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>太原基地</t>
@@ -2475,7 +3767,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>布格拉汗-斯坎旦尔</t>
@@ -2483,18 +3774,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>伤停</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>MCL撕裂·康复中</t>
@@ -2502,7 +3789,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>戚博(U21)</t>
@@ -2510,39 +3796,1948 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>FWD</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>太原基地</t>
         </is>
       </c>
     </row>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸ 2026-07-26  中乙第18轮  🏟主场 vs 南通海门珂缔缘  2-0 胜  95min  3-5-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  74′ ↑凌中阳 ↓何麟立 | 86′ ↑努尔扎提 ↑王捷 ↑阿西江 ↓巫林峰 ↓王皓文 ↓陈祥煜 | 90+3′ ↑李金羽 ↓艾沙江 | 🟡张俊哲57′·张天龙83′</t>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>首发11人 (3-5-2)</t>
+        </is>
+      </c>
+      <c r="B86" s="29" t="n"/>
+      <c r="C86" s="29" t="n"/>
+      <c r="D86" s="29" t="n"/>
+      <c r="E86" s="29" t="n"/>
+      <c r="F86" s="29" t="n"/>
+      <c r="G86" s="29" t="n"/>
+      <c r="H86" s="29" t="n"/>
+      <c r="I86" s="30" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D87" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="E87" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G87" s="27" t="n">
+        <v>855</v>
+      </c>
+      <c r="H87" s="27" t="inlineStr"/>
+      <c r="I87" s="27" t="inlineStr">
+        <is>
+          <t>脚踝D13✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B88" s="28" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D88" s="28" t="n">
+        <v>95</v>
+      </c>
+      <c r="E88" s="28" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F88" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" s="28" t="n">
+        <v>665</v>
+      </c>
+      <c r="H88" s="28" t="inlineStr"/>
+      <c r="I88" s="28" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="E89" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F89" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G89" s="27" t="n">
+        <v>855</v>
+      </c>
+      <c r="H89" s="27" t="inlineStr"/>
+      <c r="I89" s="27" t="inlineStr">
+        <is>
+          <t>🟡57′</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B90" s="28" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D90" s="28" t="n">
+        <v>95</v>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F90" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G90" s="28" t="n">
+        <v>665</v>
+      </c>
+      <c r="H90" s="28" t="inlineStr"/>
+      <c r="I90" s="28" t="inlineStr">
+        <is>
+          <t>🟡83′</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C91" s="27" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="E91" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F91" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" s="27" t="n">
+        <v>855</v>
+      </c>
+      <c r="H91" s="27" t="inlineStr"/>
+      <c r="I91" s="27" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="n">
+        <v>74</v>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F92" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" s="28" t="n">
+        <v>740</v>
+      </c>
+      <c r="H92" s="28" t="inlineStr">
+        <is>
+          <t>74′↓</t>
+        </is>
+      </c>
+      <c r="I92" s="28" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C93" s="27" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F93" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" s="27" t="n">
+        <v>860</v>
+      </c>
+      <c r="H93" s="27" t="inlineStr">
+        <is>
+          <t>86′↓</t>
+        </is>
+      </c>
+      <c r="I93" s="27" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D94" s="28" t="n">
+        <v>86</v>
+      </c>
+      <c r="E94" s="28" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F94" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" s="28" t="n">
+        <v>688</v>
+      </c>
+      <c r="H94" s="28" t="inlineStr">
+        <is>
+          <t>86′↓</t>
+        </is>
+      </c>
+      <c r="I94" s="28" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="C95" s="27" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F95" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" s="27" t="n">
+        <v>475</v>
+      </c>
+      <c r="H95" s="27" t="inlineStr"/>
+      <c r="I95" s="27" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B96" s="28" t="inlineStr">
+        <is>
+          <t>艾沙江(C)</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D96" s="28" t="n">
+        <v>93</v>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F96" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G96" s="28" t="n">
+        <v>558</v>
+      </c>
+      <c r="H96" s="28" t="inlineStr">
+        <is>
+          <t>90+3′↓</t>
+        </is>
+      </c>
+      <c r="I96" s="28" t="inlineStr">
+        <is>
+          <t>⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C97" s="27" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="E97" s="27" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="27" t="n">
+        <v>860</v>
+      </c>
+      <c r="H97" s="27" t="inlineStr">
+        <is>
+          <t>86′↓</t>
+        </is>
+      </c>
+      <c r="I97" s="27" t="inlineStr">
+        <is>
+          <t>⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>替补上场 5人</t>
+        </is>
+      </c>
+      <c r="B99" s="29" t="n"/>
+      <c r="C99" s="29" t="n"/>
+      <c r="D99" s="29" t="n"/>
+      <c r="E99" s="29" t="n"/>
+      <c r="F99" s="29" t="n"/>
+      <c r="G99" s="29" t="n"/>
+      <c r="H99" s="29" t="n"/>
+      <c r="I99" s="30" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="26" t="n"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="26" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="26" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="26" t="n"/>
+    </row>
+    <row r="104">
+      <c r="F104" s="26" t="n"/>
+    </row>
+    <row r="105">
+      <c r="G105" s="26" t="n"/>
+    </row>
+    <row r="106">
+      <c r="H106" s="26" t="n"/>
+    </row>
+    <row r="107">
+      <c r="I107" s="26" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr"/>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="E108" s="27" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F108" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" s="27" t="n">
+        <v>105</v>
+      </c>
+      <c r="H108" s="27" t="inlineStr">
+        <is>
+          <t>74′↑</t>
+        </is>
+      </c>
+      <c r="I108" s="27" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="inlineStr"/>
+      <c r="B109" s="28" t="inlineStr">
+        <is>
+          <t>努尔扎提</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D109" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E109" s="28" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F109" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="H109" s="28" t="inlineStr">
+        <is>
+          <t>86′↑</t>
+        </is>
+      </c>
+      <c r="I109" s="28" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="27" t="inlineStr"/>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E110" s="27" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F110" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="H110" s="27" t="inlineStr">
+        <is>
+          <t>86′↑</t>
+        </is>
+      </c>
+      <c r="I110" s="27" t="inlineStr">
+        <is>
+          <t>膝✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="28" t="inlineStr"/>
+      <c r="B111" s="28" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D111" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E111" s="28" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F111" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G111" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="H111" s="28" t="inlineStr">
+        <is>
+          <t>86′↑</t>
+        </is>
+      </c>
+      <c r="I111" s="28" t="inlineStr">
+        <is>
+          <t>趾骨⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr"/>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="27" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F112" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H112" s="27" t="inlineStr">
+        <is>
+          <t>90+3′↑</t>
+        </is>
+      </c>
+      <c r="I112" s="27" t="inlineStr"/>
+    </row>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>⚽ 8/1 中乙第13轮 · 主场 vs 北理工</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>首发11人</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>95</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>81</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>9</v>
+      </c>
+      <c r="G119" t="n">
+        <v>729</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>81′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>95</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>7</v>
+      </c>
+      <c r="G120" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>95</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>9</v>
+      </c>
+      <c r="G121" t="n">
+        <v>855</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>睡1疲1酸1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>90</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>9</v>
+      </c>
+      <c r="G122" t="n">
+        <v>810</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>90′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>95</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>95</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>9</v>
+      </c>
+      <c r="G124" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>72</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
+      <c r="G125" t="n">
+        <v>504</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>72′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>46</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>230</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>46′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>95</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>9</v>
+      </c>
+      <c r="G127" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>90</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>720</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>90′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>替补5人</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>49</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>8</v>
+      </c>
+      <c r="G130" t="n">
+        <v>392</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>46′↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>23</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" t="n">
+        <v>115</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>72′↑</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>趾骨已消✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>14</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
+      <c r="G132" t="n">
+        <v>98</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>81′↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>90′↑</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>右膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>25</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>90′↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>赛后大禁区跑 8×(30s/30s)=8min: 凌中阳/李金羽/努尔扎提 + 未登场替补7人(杨卓燠/王款/陈少豪/王捷/杨文杰/谢锦政/杨翼璇)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>未进大名单: 王熙博/刘子洁/布格拉汗/林楷轩/朱云天/董德/吕佳骏</t>
+        </is>
+      </c>
+    </row>
+    <row r="138"/>
+    <row r="139">
+      <c r="A139" s="31" t="inlineStr">
+        <is>
+          <t>⚽ 8/5 中乙补赛 · 客场 vs 上海海港B · 1-0 胜（95min）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="31" t="inlineStr">
+        <is>
+          <t>首发11人（8人全场+3人换下）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>95</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>10</v>
+      </c>
+      <c r="G142" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>95</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>7</v>
+      </c>
+      <c r="G143" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>95</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>9</v>
+      </c>
+      <c r="G144" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>95</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>9</v>
+      </c>
+      <c r="G145" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>95</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>10</v>
+      </c>
+      <c r="G146" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>95</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>10</v>
+      </c>
+      <c r="G147" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>95</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>10</v>
+      </c>
+      <c r="G148" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>92</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>10</v>
+      </c>
+      <c r="G149" t="n">
+        <v>920</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>90+2'↓</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>赛前3天紧→满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>92</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>10</v>
+      </c>
+      <c r="G150" t="n">
+        <v>920</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>90+2'↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>86</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>10</v>
+      </c>
+      <c r="G151" t="n">
+        <v>860</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>86'↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>71</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>8</v>
+      </c>
+      <c r="G152" t="n">
+        <v>568</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>71'↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="31" t="inlineStr">
+        <is>
+          <t>替补登场4人</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>24</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>7</v>
+      </c>
+      <c r="G154" t="n">
+        <v>168</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>71'↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>9</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>8</v>
+      </c>
+      <c r="G155" t="n">
+        <v>72</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>86'↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>9</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>90+2'↑</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>右膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>15</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>90+2'↑</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="158"/>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>赛后跑/未登场替补</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>赛后: 未登场替补(栾昊/阿西江/布格拉汗/王款/杨翼璇/谢锦政/陈少豪/杨卓燠)+未进名单(林楷轩/杨文杰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>未进大名单(到上海): 林楷轩/杨文杰</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>未到上海: 王熙博/刘子洁/朱云天/董德/吕佳骏</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A44:I44"/>
+  <mergeCells count="11">
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A83:I83"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A86:I86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/share/data/比赛记录.xlsx
+++ b/public/share/data/比赛记录.xlsx
@@ -1357,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2863,7 +2863,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -3299,7 +3298,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -3467,7 +3465,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
@@ -3810,8 +3807,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="23" t="inlineStr">
         <is>
@@ -3826,7 +3821,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="24" t="inlineStr">
         <is>
@@ -4292,7 +4286,6 @@
         </is>
       </c>
     </row>
-    <row r="98"/>
     <row r="99">
       <c r="A99" s="25" t="inlineStr">
         <is>
@@ -4505,8 +4498,6 @@
       </c>
       <c r="I112" s="27" t="inlineStr"/>
     </row>
-    <row r="113"/>
-    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -5111,7 +5102,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
@@ -5126,7 +5116,6 @@
         </is>
       </c>
     </row>
-    <row r="138"/>
     <row r="139">
       <c r="A139" s="31" t="inlineStr">
         <is>
@@ -5695,7 +5684,6 @@
         </is>
       </c>
     </row>
-    <row r="158"/>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
@@ -5710,7 +5698,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -5722,6 +5709,894 @@
       <c r="A163" t="inlineStr">
         <is>
           <t>未到上海: 王熙博/刘子洁/朱云天/董德/吕佳骏</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>⚽ 8/9 中乙第18轮 · 客场 vs 长春喜都 · 2-1 胜（95min）· 5-4-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>首发11人 (5-4-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>95</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>8</v>
+      </c>
+      <c r="G168" t="n">
+        <v>760</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>95</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>8</v>
+      </c>
+      <c r="G169" t="n">
+        <v>760</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>84</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>8</v>
+      </c>
+      <c r="G170" t="n">
+        <v>672</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>84'↓</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>95</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>10</v>
+      </c>
+      <c r="G171" t="n">
+        <v>950</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>95</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>8</v>
+      </c>
+      <c r="G172" t="n">
+        <v>760</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>95</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>8</v>
+      </c>
+      <c r="G173" t="n">
+        <v>760</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>55</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>8</v>
+      </c>
+      <c r="G174" t="n">
+        <v>440</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>55'↓</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>95</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>10</v>
+      </c>
+      <c r="G175" t="n">
+        <v>950</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>95</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>9</v>
+      </c>
+      <c r="G176" t="n">
+        <v>855</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>95</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>9</v>
+      </c>
+      <c r="G177" t="n">
+        <v>855</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>95</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>9</v>
+      </c>
+      <c r="G178" t="n">
+        <v>855</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>替补登场2人</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>40</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>8</v>
+      </c>
+      <c r="G180" t="n">
+        <v>320</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>55'↑</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>6</v>
+      </c>
+      <c r="G181" t="n">
+        <v>66</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>84'↑</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>替补未登场10人（各15min热身）</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>15</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>4</v>
+      </c>
+      <c r="G183" t="n">
+        <v>60</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>15</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>4</v>
+      </c>
+      <c r="G184" t="n">
+        <v>60</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>15</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>3</v>
+      </c>
+      <c r="G185" t="n">
+        <v>45</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>15</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>3</v>
+      </c>
+      <c r="G186" t="n">
+        <v>45</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>15</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>4</v>
+      </c>
+      <c r="G187" t="n">
+        <v>60</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>15</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>4</v>
+      </c>
+      <c r="G188" t="n">
+        <v>60</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>15</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>3</v>
+      </c>
+      <c r="G189" t="n">
+        <v>45</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>MCL恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>15</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>3</v>
+      </c>
+      <c r="G190" t="n">
+        <v>45</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>15</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>3</v>
+      </c>
+      <c r="G191" t="n">
+        <v>45</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>15</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>4</v>
+      </c>
+      <c r="G192" t="n">
+        <v>60</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>未进名单: 谢锦政(脚趾肿)/林楷轩(单独训练)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>未随队: 王熙博/刘子洁/朱云天/董德/吕佳骏</t>
         </is>
       </c>
     </row>

--- a/public/share/data/比赛记录.xlsx
+++ b/public/share/data/比赛记录.xlsx
@@ -1357,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5803,8 +5803,6 @@
       <c r="G168" t="n">
         <v>760</v>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5836,8 +5834,6 @@
       <c r="G169" t="n">
         <v>760</v>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5874,7 +5870,6 @@
           <t>84'↓</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5906,7 +5901,6 @@
       <c r="G171" t="n">
         <v>950</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>RPE=10</t>
@@ -5943,8 +5937,6 @@
       <c r="G172" t="n">
         <v>760</v>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5976,8 +5968,6 @@
       <c r="G173" t="n">
         <v>760</v>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6014,7 +6004,6 @@
           <t>55'↓</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6046,7 +6035,6 @@
       <c r="G175" t="n">
         <v>950</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>RPE=10</t>
@@ -6083,8 +6071,6 @@
       <c r="G176" t="n">
         <v>855</v>
       </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6116,8 +6102,6 @@
       <c r="G177" t="n">
         <v>855</v>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6149,7 +6133,6 @@
       <c r="G178" t="n">
         <v>855</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>⚽</t>
@@ -6239,7 +6222,6 @@
           <t>84'↑</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6278,8 +6260,6 @@
       <c r="G183" t="n">
         <v>60</v>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,8 +6291,6 @@
       <c r="G184" t="n">
         <v>60</v>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6344,7 +6322,6 @@
       <c r="G185" t="n">
         <v>45</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>左膝</t>
@@ -6381,8 +6358,6 @@
       <c r="G186" t="n">
         <v>45</v>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6414,8 +6389,6 @@
       <c r="G187" t="n">
         <v>60</v>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6447,8 +6420,6 @@
       <c r="G188" t="n">
         <v>60</v>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6480,7 +6451,6 @@
       <c r="G189" t="n">
         <v>45</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>MCL恢复</t>
@@ -6517,8 +6487,6 @@
       <c r="G190" t="n">
         <v>45</v>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6550,8 +6518,6 @@
       <c r="G191" t="n">
         <v>45</v>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6583,8 +6549,6 @@
       <c r="G192" t="n">
         <v>60</v>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6597,6 +6561,1000 @@
       <c r="A194" t="inlineStr">
         <is>
           <t>未随队: 王熙博/刘子洁/朱云天/董德/吕佳骏</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>⚽ 8/15 中乙第21轮 · 客场 vs 青岛红狮 · 0-1 负（90min）· 5-3-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>出场</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>首/替</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>换人</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>首发11人 (5-3-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>13</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>90</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>8</v>
+      </c>
+      <c r="G199" t="n">
+        <v>720</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>脚踝坚持</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>60</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>90</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>10</v>
+      </c>
+      <c r="G200" t="n">
+        <v>900</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>39</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>90</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>8</v>
+      </c>
+      <c r="G201" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>30</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>63</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>7</v>
+      </c>
+      <c r="G202" t="n">
+        <v>441</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>63′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>24</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>90</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>8</v>
+      </c>
+      <c r="G203" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>16</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>90</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>8</v>
+      </c>
+      <c r="G204" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>55</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>79</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>9</v>
+      </c>
+      <c r="G205" t="n">
+        <v>711</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>79′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>19</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>56</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>8</v>
+      </c>
+      <c r="G206" t="n">
+        <v>448</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>56′↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>33</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>90</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>9</v>
+      </c>
+      <c r="G207" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>7</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>90</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>9</v>
+      </c>
+      <c r="G208" t="n">
+        <v>810</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>队长</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>9</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>90</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>首发</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>10</v>
+      </c>
+      <c r="G209" t="n">
+        <v>900</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>替补登场3人</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>10</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>27</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+      <c r="G211" t="n">
+        <v>189</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>63′↑</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>MCL首秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>14</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>34</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+      <c r="G212" t="n">
+        <v>238</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>56′↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>11</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>8</v>
+      </c>
+      <c r="G213" t="n">
+        <v>88</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>79′↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>替补未登场9人（各15min热身）</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>31</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>15</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>3</v>
+      </c>
+      <c r="G215" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>15</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>15</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>3</v>
+      </c>
+      <c r="G216" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>28</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>15</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>3</v>
+      </c>
+      <c r="G217" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>22</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>15</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>3</v>
+      </c>
+      <c r="G218" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>15</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>3</v>
+      </c>
+      <c r="G219" t="n">
+        <v>45</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>5</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>15</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>4</v>
+      </c>
+      <c r="G220" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>8</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>15</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>23</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>15</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>15</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>未随队/未跟队7人</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>38</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>黄牌停赛·未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>26</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>27</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>20</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>未随队</t>
         </is>
       </c>
     </row>
